--- a/practice/answers/s1_q15.xlsx
+++ b/practice/answers/s1_q15.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Answer" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Answer" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,45 +28,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
       <b val="1"/>
-      <color rgb="004A7C59"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="005C6B62"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="0024302A"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Consolas"/>
-      <color rgb="002F5D46"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="0024302A"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="005C6B62"/>
-      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -75,12 +40,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004A7C59"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F6EFD9"/>
+        <fgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CFE2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D2E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -96,35 +76,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -490,195 +463,222 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>A blended price</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Total revenue over total tonnes gives the price the farm actually received. The plain average of the three grade prices treats the grades as equal.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1"/>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
           <t>Grade</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Tonnes</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Price ($/t)</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>The formula in D</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>No. 1</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B2" s="3" t="n">
         <v>1240</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C2" s="4" t="n">
         <v>14.85</v>
       </c>
-      <c r="D5" s="8">
-        <f>B5*C5</f>
-        <v/>
-      </c>
-      <c r="E5" s="9">
-        <f>_xlfn.FORMULATEXT(D5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="D2" s="5">
+        <f>B2*C2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>No. 2</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B3" s="3" t="n">
         <v>860</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C3" s="4" t="n">
         <v>13.4</v>
       </c>
-      <c r="D6" s="8">
-        <f>B6*C6</f>
-        <v/>
-      </c>
-      <c r="E6" s="9">
-        <f>_xlfn.FORMULATEXT(D6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="D3" s="5">
+        <f>B3*C3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Sample</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B4" s="3" t="n">
         <v>410</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C4" s="4" t="n">
         <v>10.75</v>
       </c>
-      <c r="D7" s="8">
-        <f>B7*C7</f>
-        <v/>
-      </c>
-      <c r="E7" s="9">
-        <f>_xlfn.FORMULATEXT(D7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="D4" s="5">
+        <f>B4*C4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B8" s="11">
-        <f>SUM(B5:B7)</f>
-        <v/>
-      </c>
-      <c r="D8" s="12">
-        <f>SUM(D5:D7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1"/>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>Blended: revenue / tonnes</t>
-        </is>
-      </c>
-      <c r="C10" s="8">
-        <f>D8/B8</f>
-        <v/>
-      </c>
-      <c r="E10" s="9">
-        <f>_xlfn.FORMULATEXT(C10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Blended: SUMPRODUCT</t>
-        </is>
-      </c>
-      <c r="C11" s="8">
-        <f>SUMPRODUCT(B5:B7,C5:C7)/SUM(B5:B7)</f>
-        <v/>
-      </c>
-      <c r="E11" s="9">
-        <f>_xlfn.FORMULATEXT(C11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>AVERAGE of the price column</t>
-        </is>
-      </c>
-      <c r="C12" s="8">
-        <f>AVERAGE(C5:C7)</f>
-        <v/>
-      </c>
-      <c r="E12" s="9">
-        <f>_xlfn.FORMULATEXT(C12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1"/>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>$13.68 against $13.00. The two blended routes agree, which is the check. The plain average treats Sample -- 410 of 2,510 tonnes -- as equal in weight to No. 1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1"/>
+      <c r="B5" s="6">
+        <f>SUM(B2:B4)</f>
+        <v/>
+      </c>
+      <c r="D5" s="5">
+        <f>SUM(D2:D4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Blended price ($/t)</t>
+        </is>
+      </c>
+      <c r="B7" s="8">
+        <f>D5/B5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>SUMPRODUCT over SUM</t>
+        </is>
+      </c>
+      <c r="B8" s="10">
+        <f>SUMPRODUCT(B2:B4,C2:C4)/SUM(B2:B4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>AVERAGE of prices</t>
+        </is>
+      </c>
+      <c r="B9" s="12">
+        <f>AVERAGE(C2:C4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>The plain average of the three prices is $13.00; the blended price is $13.68. The blended price describes what the farm received, because it counts every tonne once.</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="n"/>
+      <c r="C11" s="11" t="n"/>
+      <c r="D11" s="11" t="n"/>
+      <c r="E11" s="11" t="n"/>
+      <c r="F11" s="11" t="n"/>
+      <c r="G11" s="11" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="n"/>
+      <c r="B12" s="11" t="n"/>
+      <c r="C12" s="11" t="n"/>
+      <c r="D12" s="11" t="n"/>
+      <c r="E12" s="11" t="n"/>
+      <c r="F12" s="11" t="n"/>
+      <c r="G12" s="11" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>It treats each grade as equally important, even though No. 1 accounts for nearly half the tonnage and Sample for about a sixth.</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="n"/>
+      <c r="C14" s="15" t="n"/>
+      <c r="D14" s="15" t="n"/>
+      <c r="E14" s="15" t="n"/>
+      <c r="F14" s="15" t="n"/>
+      <c r="G14" s="15" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="n"/>
+      <c r="B15" s="15" t="n"/>
+      <c r="C15" s="15" t="n"/>
+      <c r="D15" s="15" t="n"/>
+      <c r="E15" s="15" t="n"/>
+      <c r="F15" s="15" t="n"/>
+      <c r="G15" s="15" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>Part (a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Part (b)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>Part (c)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>Part (d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>Part (e)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A14:G15"/>
+    <mergeCell ref="A11:G12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/practice/answers/s1_q15.xlsx
+++ b/practice/answers/s1_q15.xlsx
@@ -16,8 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="$0.000"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -31,7 +32,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -58,11 +59,6 @@
         <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9D2E9"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -76,28 +72,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -463,16 +453,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -491,9 +478,9 @@
           <t>Price ($/t)</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Revenue</t>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Revenue ($) (a)</t>
         </is>
       </c>
     </row>
@@ -503,13 +490,13 @@
           <t>No. 1</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" t="n">
         <v>1240</v>
       </c>
-      <c r="C2" s="4" t="n">
+      <c r="C2" s="2" t="n">
         <v>14.85</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="3">
         <f>B2*C2</f>
         <v/>
       </c>
@@ -520,13 +507,13 @@
           <t>No. 2</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B3" t="n">
         <v>860</v>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C3" s="2" t="n">
         <v>13.4</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="3">
         <f>B3*C3</f>
         <v/>
       </c>
@@ -537,148 +524,110 @@
           <t>Sample</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" t="n">
         <v>410</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="2" t="n">
         <v>10.75</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="3">
         <f>B4*C4</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B5" s="6">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Totals (a)</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
         <f>SUM(B2:B4)</f>
         <v/>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="3">
         <f>SUM(D2:D4)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Blended price ($/t)</t>
-        </is>
-      </c>
-      <c r="B7" s="8">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Blended price (b):</t>
+        </is>
+      </c>
+      <c r="B7" s="5">
         <f>D5/B5</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>SUMPRODUCT over SUM</t>
-        </is>
-      </c>
-      <c r="B8" s="10">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Blended, one cell (c):</t>
+        </is>
+      </c>
+      <c r="B8" s="6">
         <f>SUMPRODUCT(B2:B4,C2:C4)/SUM(B2:B4)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>AVERAGE of prices</t>
-        </is>
-      </c>
-      <c r="B9" s="12">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Plain AVERAGE (d):</t>
+        </is>
+      </c>
+      <c r="B9" s="7">
         <f>AVERAGE(C2:C4)</f>
         <v/>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>The plain average of the three prices is $13.00; the blended price is $13.68. The blended price describes what the farm received, because it counts every tonne once.</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="n"/>
-      <c r="C11" s="11" t="n"/>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="11" t="n"/>
-      <c r="F11" s="11" t="n"/>
-      <c r="G11" s="11" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="n"/>
-      <c r="B12" s="11" t="n"/>
-      <c r="C12" s="11" t="n"/>
-      <c r="D12" s="11" t="n"/>
-      <c r="E12" s="11" t="n"/>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="n"/>
+    <row r="11" ht="45" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>(d) The blended price (about $13.68/t) is what the farm actually received: total dollars over total tonnes. The plain average (about $13.00/t) treats the 410-tonne Sample load the same as the 1,240-tonne No. 1 load, so the low Sample price counts far more than its share of the grain -- the two differ whenever tonnage is uneven across prices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Legend: colours mark question parts</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>It treats each grade as equally important, even though No. 1 accounts for nearly half the tonnage and Sample for about a sixth.</t>
-        </is>
-      </c>
-      <c r="B14" s="15" t="n"/>
-      <c r="C14" s="15" t="n"/>
-      <c r="D14" s="15" t="n"/>
-      <c r="E14" s="15" t="n"/>
-      <c r="F14" s="15" t="n"/>
-      <c r="G14" s="15" t="n"/>
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>Part (a)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="n"/>
-      <c r="B15" s="15" t="n"/>
-      <c r="C15" s="15" t="n"/>
-      <c r="D15" s="15" t="n"/>
-      <c r="E15" s="15" t="n"/>
-      <c r="F15" s="15" t="n"/>
-      <c r="G15" s="15" t="n"/>
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Part (b)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>Part (c)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="inlineStr">
-        <is>
-          <t>Part (a)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Part (b)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>Part (c)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>Part (d)</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>Part (e)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A14:G15"/>
-    <mergeCell ref="A11:G12"/>
+  <mergeCells count="1">
+    <mergeCell ref="A11:F11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/practice/answers/s1_q15.xlsx
+++ b/practice/answers/s1_q15.xlsx
@@ -583,7 +583,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="45" customHeight="1">
+    <row r="11" ht="64" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>(d) The blended price (about $13.68/t) is what the farm actually received: total dollars over total tonnes. The plain average (about $13.00/t) treats the 410-tonne Sample load the same as the 1,240-tonne No. 1 load, so the low Sample price counts far more than its share of the grain -- the two differ whenever tonnage is uneven across prices.</t>

--- a/practice/answers/s1_q15.xlsx
+++ b/practice/answers/s1_q15.xlsx
@@ -470,12 +470,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Tonnes</t>
+          <t>Bushels</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Price ($/t)</t>
+          <t>Price ($/bu)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -550,6 +550,7 @@
         <v/>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
@@ -583,13 +584,15 @@
         <v/>
       </c>
     </row>
+    <row r="10"/>
     <row r="11" ht="64" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>(d) The blended price (about $13.68/t) is what the farm actually received: total dollars over total tonnes. The plain average (about $13.00/t) treats the 410-tonne Sample load the same as the 1,240-tonne No. 1 load, so the low Sample price counts far more than its share of the grain -- the two differ whenever tonnage is uneven across prices.</t>
-        </is>
-      </c>
-    </row>
+          <t>(d) The blended price (about $13.68/t) is what the farm actually received: total dollars over total bushels. The plain average (about $13.00/t) treats the 410-tonne Sample load the same as the 1,240-tonne No. 1 load, so the low Sample price counts far more than its share of the grain -- the two differ whenever tonnage is uneven across prices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>

--- a/practice/answers/s1_q15.xlsx
+++ b/practice/answers/s1_q15.xlsx
@@ -470,12 +470,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Bushels</t>
+          <t>Tonnes</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Price ($/bu)</t>
+          <t>Price ($/t)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -550,7 +550,6 @@
         <v/>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
@@ -584,15 +583,13 @@
         <v/>
       </c>
     </row>
-    <row r="10"/>
     <row r="11" ht="64" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>(d) The blended price (about $13.68/t) is what the farm actually received: total dollars over total bushels. The plain average (about $13.00/t) treats the 410-tonne Sample load the same as the 1,240-tonne No. 1 load, so the low Sample price counts far more than its share of the grain -- the two differ whenever tonnage is uneven across prices.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
+          <t>(d) The blended price (about $13.68/t) is what the farm actually received: total dollars over total tonnes. The plain average (about $13.00/t) treats the 410-tonne Sample load the same as the 1,240-tonne No. 1 load, so the low Sample price counts far more than its share of the grain -- the two differ whenever tonnage is uneven across prices.</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
